--- a/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_08.xlsx
+++ b/Voti_Fantacalcio/Voti_Fantacalcio_Stagione_2023_24_Giornata_08.xlsx
@@ -658,7 +658,7 @@
     <t>Krstovic</t>
   </si>
   <si>
-    <t>D'aversa</t>
+    <t>D'Aversa</t>
   </si>
   <si>
     <t>Milan</t>
@@ -721,7 +721,7 @@
     <t>Di Gregorio</t>
   </si>
   <si>
-    <t>D'ambrosio</t>
+    <t>D'Ambrosio</t>
   </si>
   <si>
     <t>Pereira P.</t>
@@ -805,7 +805,7 @@
     <t>Lindstrom</t>
   </si>
   <si>
-    <t xml:space="preserve">Cajuste </t>
+    <t>Cajuste</t>
   </si>
   <si>
     <t>Simeone</t>
@@ -838,7 +838,7 @@
     <t>Mancini</t>
   </si>
   <si>
-    <t>N'dicka</t>
+    <t>N'Dicka</t>
   </si>
   <si>
     <t>Celik</t>
